--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486949_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486949_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.5291</v>
+        <v>4.3135</v>
       </c>
       <c r="E2" t="n">
-        <v>4.2991</v>
+        <v>4.7059</v>
       </c>
       <c r="F2" t="n">
-        <v>0.2301</v>
+        <v>-0.3924</v>
       </c>
       <c r="G2" t="n">
         <v>-0.6183</v>
@@ -610,13 +610,13 @@
         <v>1.4374</v>
       </c>
       <c r="S2" t="n">
-        <v>0.9606</v>
+        <v>0.7449</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.4225</v>
+        <v>-0.0156</v>
       </c>
       <c r="U2" t="n">
-        <v>1.3831</v>
+        <v>0.7606000000000001</v>
       </c>
       <c r="V2" t="n">
         <v>3.7761</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.3605</v>
+        <v>3.3365</v>
       </c>
       <c r="E3" t="n">
-        <v>3.8602</v>
+        <v>4.6582</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.4996</v>
+        <v>-1.3218</v>
       </c>
       <c r="G3" t="n">
         <v>-0.6477000000000001</v>
@@ -688,13 +688,13 @@
         <v>1.0267</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.4393</v>
+        <v>0.5366</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.9145</v>
+        <v>-0.1164</v>
       </c>
       <c r="U3" t="n">
-        <v>0.4752</v>
+        <v>0.653</v>
       </c>
       <c r="V3" t="n">
         <v>4.4743</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.5765</v>
+        <v>0.6563</v>
       </c>
       <c r="E4" t="n">
-        <v>4.8076</v>
+        <v>4.7688</v>
       </c>
       <c r="F4" t="n">
-        <v>-4.231</v>
+        <v>-4.1125</v>
       </c>
       <c r="G4" t="n">
         <v>1.9672</v>
@@ -766,13 +766,13 @@
         <v>1.0267</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.169</v>
+        <v>-0.0891</v>
       </c>
       <c r="T4" t="n">
-        <v>0.1704</v>
+        <v>0.1316</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.3394</v>
+        <v>-0.2208</v>
       </c>
       <c r="V4" t="n">
         <v>-2.2484</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>C. TOLEDO ZAMORA</t>
+          <t>F. HERNANDEZ MARTINEZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,64 +799,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.1389</v>
+        <v>-0.1469</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.08</v>
+        <v>-0.1259</v>
       </c>
       <c r="F5" t="n">
-        <v>0.2189</v>
+        <v>-0.021</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.4237</v>
+        <v>-0.5479000000000001</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.2554</v>
+        <v>-1.8135</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.1682</v>
+        <v>1.2656</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.5216</v>
+        <v>1.703</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.5611</v>
+        <v>0.0458</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0395</v>
+        <v>1.6572</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.902</v>
+        <v>-2.2509</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.6943</v>
+        <v>-1.8593</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.2077</v>
+        <v>-0.3916</v>
       </c>
       <c r="P5" t="n">
-        <v>0.2053</v>
+        <v>-0.4107</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-2.0534</v>
       </c>
       <c r="R5" t="n">
-        <v>0.2053</v>
+        <v>1.6427</v>
       </c>
       <c r="S5" t="n">
-        <v>1.3572</v>
+        <v>0.5715</v>
       </c>
       <c r="T5" t="n">
-        <v>0.4416</v>
+        <v>-0.0156</v>
       </c>
       <c r="U5" t="n">
-        <v>0.9156</v>
+        <v>0.5872000000000001</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>0.2402</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>0.2402</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. TAVELLI</t>
+          <t>C. TOLEDO ZAMORA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.1859</v>
+        <v>-0.2778</v>
       </c>
       <c r="E6" t="n">
-        <v>1.8232</v>
+        <v>-0.2892</v>
       </c>
       <c r="F6" t="n">
-        <v>-2.0091</v>
+        <v>0.0114</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0517</v>
+        <v>-1.4237</v>
       </c>
       <c r="H6" t="n">
-        <v>0.3701</v>
+        <v>-1.2554</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.3184</v>
+        <v>-0.1682</v>
       </c>
       <c r="J6" t="n">
-        <v>1.9086</v>
+        <v>-0.5216</v>
       </c>
       <c r="K6" t="n">
-        <v>1.3694</v>
+        <v>-0.5611</v>
       </c>
       <c r="L6" t="n">
-        <v>0.5391</v>
+        <v>0.0395</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.8569</v>
+        <v>-0.902</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.9994</v>
+        <v>-0.6943</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.8575</v>
+        <v>-0.2077</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.616</v>
+        <v>0.2053</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.0267</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0.4107</v>
+        <v>0.2053</v>
       </c>
       <c r="S6" t="n">
-        <v>1.208</v>
+        <v>0.9405</v>
       </c>
       <c r="T6" t="n">
-        <v>0.9413</v>
+        <v>0.2324</v>
       </c>
       <c r="U6" t="n">
-        <v>0.2667</v>
+        <v>0.7081</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.8295</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.8295</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.2505</v>
+        <v>-0.5347</v>
       </c>
       <c r="E7" t="n">
-        <v>0.9318</v>
+        <v>0.618</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.1823</v>
+        <v>-1.1527</v>
       </c>
       <c r="G7" t="n">
         <v>0.183</v>
@@ -1000,13 +1000,13 @@
         <v>0.616</v>
       </c>
       <c r="S7" t="n">
-        <v>0.2174</v>
+        <v>-0.0668</v>
       </c>
       <c r="T7" t="n">
-        <v>0.2362</v>
+        <v>-0.0776</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.0189</v>
+        <v>0.0108</v>
       </c>
       <c r="V7" t="n">
         <v>-0.2402</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.4701</v>
+        <v>-0.6974</v>
       </c>
       <c r="E8" t="n">
-        <v>0.3794</v>
+        <v>0.09279999999999999</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.8495</v>
+        <v>-0.7902</v>
       </c>
       <c r="G8" t="n">
         <v>-1.1488</v>
@@ -1078,13 +1078,13 @@
         <v>0.2053</v>
       </c>
       <c r="S8" t="n">
-        <v>0.4734</v>
+        <v>0.246</v>
       </c>
       <c r="T8" t="n">
-        <v>0.4339</v>
+        <v>0.1472</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0395</v>
+        <v>0.0988</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>F. HERNANDEZ MARTINEZ</t>
+          <t>G. MILADINOVIC</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.6657</v>
+        <v>-0.8572</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.4668</v>
+        <v>0.6587</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.1989</v>
+        <v>-1.5158</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.5479000000000001</v>
+        <v>-1.0557</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.8135</v>
+        <v>-0.3534</v>
       </c>
       <c r="I9" t="n">
-        <v>1.2656</v>
+        <v>-0.7023</v>
       </c>
       <c r="J9" t="n">
-        <v>1.703</v>
+        <v>0.8249</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0458</v>
+        <v>0.7855</v>
       </c>
       <c r="L9" t="n">
-        <v>1.6572</v>
+        <v>0.0395</v>
       </c>
       <c r="M9" t="n">
-        <v>-2.2509</v>
+        <v>-1.8807</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.8593</v>
+        <v>-1.1389</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.3916</v>
+        <v>-0.7418</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.4107</v>
+        <v>-0.616</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.0534</v>
+        <v>-1.0267</v>
       </c>
       <c r="R9" t="n">
-        <v>1.6427</v>
+        <v>0.4107</v>
       </c>
       <c r="S9" t="n">
-        <v>0.0527</v>
+        <v>0.8146</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.3566</v>
+        <v>0.2711</v>
       </c>
       <c r="U9" t="n">
-        <v>0.4093</v>
+        <v>0.5434</v>
       </c>
       <c r="V9" t="n">
-        <v>0.2402</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>0.2402</v>
+        <v>0.5893</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-0.5893</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.928</v>
+        <v>-0.8984</v>
       </c>
       <c r="E10" t="n">
         <v>-0.4481</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.4799</v>
+        <v>-0.4503</v>
       </c>
       <c r="G10" t="n">
         <v>0.1448</v>
@@ -1234,13 +1234,13 @@
         <v>0.2053</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.2515</v>
+        <v>-0.2218</v>
       </c>
       <c r="T10" t="n">
         <v>-0.1317</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.1197</v>
+        <v>-0.0901</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>G. MILADINOVIC</t>
+          <t>J. TAVELLI</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,40 +1267,40 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.9733000000000001</v>
+        <v>-0.9774</v>
       </c>
       <c r="E11" t="n">
-        <v>0.6315</v>
+        <v>1.091</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.6048</v>
+        <v>-2.0684</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.0557</v>
+        <v>0.0517</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.3534</v>
+        <v>0.3701</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.7023</v>
+        <v>-0.3184</v>
       </c>
       <c r="J11" t="n">
-        <v>0.8249</v>
+        <v>1.9086</v>
       </c>
       <c r="K11" t="n">
-        <v>0.7855</v>
+        <v>1.3694</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0395</v>
+        <v>0.5391</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.8807</v>
+        <v>-1.8569</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.1389</v>
+        <v>-0.9994</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.7418</v>
+        <v>-0.8575</v>
       </c>
       <c r="P11" t="n">
         <v>-0.616</v>
@@ -1312,22 +1312,22 @@
         <v>0.4107</v>
       </c>
       <c r="S11" t="n">
-        <v>0.6985</v>
+        <v>0.4165</v>
       </c>
       <c r="T11" t="n">
-        <v>0.244</v>
+        <v>0.2091</v>
       </c>
       <c r="U11" t="n">
-        <v>0.4545</v>
+        <v>0.2074</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>-0.8295</v>
       </c>
       <c r="W11" t="n">
-        <v>0.5893</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.5893</v>
+        <v>-0.8295</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-5.0488</v>
+        <v>-4.4756</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.2262</v>
+        <v>-1.7419</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.8226</v>
+        <v>-2.7336</v>
       </c>
       <c r="G12" t="n">
         <v>-7.5114</v>
@@ -1390,13 +1390,13 @@
         <v>0.8214</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.6072</v>
+        <v>-0.034</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.7827</v>
+        <v>-0.2985</v>
       </c>
       <c r="U12" t="n">
-        <v>0.1756</v>
+        <v>0.2645</v>
       </c>
       <c r="V12" t="n">
         <v>2.2484</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-7.4133</v>
+        <v>-6.7834</v>
       </c>
       <c r="E13" t="n">
-        <v>-5.3067</v>
+        <v>-4.7953</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.1066</v>
+        <v>-1.9881</v>
       </c>
       <c r="G13" t="n">
         <v>-3.5475</v>
@@ -1468,13 +1468,13 @@
         <v>1.2321</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.0527</v>
+        <v>0.5773</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.4225</v>
+        <v>0.089</v>
       </c>
       <c r="U13" t="n">
-        <v>0.3698</v>
+        <v>0.4883</v>
       </c>
       <c r="V13" t="n">
         <v>-0.9384</v>
@@ -1501,31 +1501,31 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-8.3306</v>
+        <v>-7.3425</v>
       </c>
       <c r="E14" t="n">
-        <v>8.204999999999998</v>
+        <v>9.193000000000001</v>
       </c>
       <c r="F14" t="n">
-        <v>-16.5353</v>
+        <v>-16.5354</v>
       </c>
       <c r="G14" t="n">
         <v>-14.1543</v>
       </c>
       <c r="H14" t="n">
-        <v>-8.3531</v>
+        <v>-8.353100000000001</v>
       </c>
       <c r="I14" t="n">
         <v>-5.801</v>
       </c>
       <c r="J14" t="n">
-        <v>9.476999999999999</v>
+        <v>9.477</v>
       </c>
       <c r="K14" t="n">
         <v>5.664299999999998</v>
       </c>
       <c r="L14" t="n">
-        <v>3.812699999999999</v>
+        <v>3.812700000000001</v>
       </c>
       <c r="M14" t="n">
         <v>-23.6311</v>
@@ -1546,13 +1546,13 @@
         <v>9.240300000000001</v>
       </c>
       <c r="S14" t="n">
-        <v>3.4481</v>
+        <v>4.4362</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.5631</v>
+        <v>0.4249999999999998</v>
       </c>
       <c r="U14" t="n">
-        <v>4.0113</v>
+        <v>4.0112</v>
       </c>
       <c r="V14" t="n">
         <v>6.482500000000001</v>
@@ -1561,7 +1561,7 @@
         <v>12.6382</v>
       </c>
       <c r="X14" t="n">
-        <v>-6.1558</v>
+        <v>-6.155800000000001</v>
       </c>
     </row>
     <row r="15">
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>9.6066</v>
+        <v>9.882</v>
       </c>
       <c r="E15" t="n">
-        <v>7.9465</v>
+        <v>8.260300000000001</v>
       </c>
       <c r="F15" t="n">
-        <v>1.6601</v>
+        <v>1.6217</v>
       </c>
       <c r="G15" t="n">
         <v>6.5821</v>
@@ -1624,13 +1624,13 @@
         <v>2.6694</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.8236</v>
+        <v>-0.5482</v>
       </c>
       <c r="T15" t="n">
-        <v>-1.0889</v>
+        <v>-0.7751</v>
       </c>
       <c r="U15" t="n">
-        <v>0.2653</v>
+        <v>0.2269</v>
       </c>
       <c r="V15" t="n">
         <v>1.1786</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.7077</v>
+        <v>3.3556</v>
       </c>
       <c r="E16" t="n">
-        <v>5.98</v>
+        <v>5.6662</v>
       </c>
       <c r="F16" t="n">
-        <v>-2.2723</v>
+        <v>-2.3106</v>
       </c>
       <c r="G16" t="n">
         <v>2.6522</v>
@@ -1702,13 +1702,13 @@
         <v>1.4374</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.0759</v>
+        <v>-0.4281</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.0854</v>
+        <v>-0.3992</v>
       </c>
       <c r="U16" t="n">
-        <v>0.0095</v>
+        <v>-0.0289</v>
       </c>
       <c r="V16" t="n">
         <v>0.7207</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.5398</v>
+        <v>2.8431</v>
       </c>
       <c r="E17" t="n">
-        <v>2.3097</v>
+        <v>2.4143</v>
       </c>
       <c r="F17" t="n">
-        <v>0.2301</v>
+        <v>0.4288</v>
       </c>
       <c r="G17" t="n">
         <v>4.783</v>
@@ -1780,13 +1780,13 @@
         <v>1.8481</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.3397</v>
+        <v>-1.0364</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.1044</v>
+        <v>-0.9998</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.2354</v>
+        <v>-0.0366</v>
       </c>
       <c r="V17" t="n">
         <v>-0.6982</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.1107</v>
+        <v>-0.217</v>
       </c>
       <c r="E18" t="n">
-        <v>3.945</v>
+        <v>3.6312</v>
       </c>
       <c r="F18" t="n">
-        <v>-4.0557</v>
+        <v>-3.8482</v>
       </c>
       <c r="G18" t="n">
         <v>3.3029</v>
@@ -1858,13 +1858,13 @@
         <v>1.4374</v>
       </c>
       <c r="S18" t="n">
-        <v>0.301</v>
+        <v>0.1947</v>
       </c>
       <c r="T18" t="n">
-        <v>0.2594</v>
+        <v>-0.0544</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0416</v>
+        <v>0.249</v>
       </c>
       <c r="V18" t="n">
         <v>-4.1252</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.3831</v>
+        <v>-0.5906</v>
       </c>
       <c r="E19" t="n">
         <v>-0.6781</v>
       </c>
       <c r="F19" t="n">
-        <v>0.295</v>
+        <v>0.08749999999999999</v>
       </c>
       <c r="G19" t="n">
         <v>1.7862</v>
@@ -1936,13 +1936,13 @@
         <v>1.0267</v>
       </c>
       <c r="S19" t="n">
-        <v>0.0361</v>
+        <v>-0.1714</v>
       </c>
       <c r="T19" t="n">
         <v>-0.1822</v>
       </c>
       <c r="U19" t="n">
-        <v>0.2183</v>
+        <v>0.0108</v>
       </c>
       <c r="V19" t="n">
         <v>-1.1786</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.7072000000000001</v>
+        <v>-0.6288</v>
       </c>
       <c r="E20" t="n">
-        <v>2.0171</v>
+        <v>1.8079</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.7244</v>
+        <v>-2.4367</v>
       </c>
       <c r="G20" t="n">
         <v>0.3371</v>
@@ -2014,13 +2014,13 @@
         <v>1.6427</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.6994</v>
+        <v>-0.6209</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.4729</v>
+        <v>-0.6821</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.2265</v>
+        <v>0.0612</v>
       </c>
       <c r="V20" t="n">
         <v>-0.9609</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.8561</v>
+        <v>-0.7218</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.0723</v>
+        <v>0.0323</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.7838000000000001</v>
+        <v>-0.7541</v>
       </c>
       <c r="G21" t="n">
         <v>-0.5387999999999999</v>
@@ -2092,13 +2092,13 @@
         <v>0.616</v>
       </c>
       <c r="S21" t="n">
-        <v>0.0934</v>
+        <v>0.2276</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.248</v>
+        <v>-0.1434</v>
       </c>
       <c r="U21" t="n">
-        <v>0.3414</v>
+        <v>0.371</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.5848</v>
+        <v>-1.1088</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.8049</v>
+        <v>-1.5957</v>
       </c>
       <c r="F22" t="n">
-        <v>0.2201</v>
+        <v>0.4868</v>
       </c>
       <c r="G22" t="n">
         <v>-0.9443</v>
@@ -2170,13 +2170,13 @@
         <v>2.0534</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.4886</v>
+        <v>-0.0126</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.4961</v>
+        <v>-0.2869</v>
       </c>
       <c r="U22" t="n">
-        <v>0.0075</v>
+        <v>0.2743</v>
       </c>
       <c r="V22" t="n">
         <v>-1.1786</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.8816</v>
+        <v>-3.7858</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.1076</v>
+        <v>-3.003</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.7741</v>
+        <v>-0.7828000000000001</v>
       </c>
       <c r="G23" t="n">
         <v>-3.8061</v>
@@ -2248,13 +2248,13 @@
         <v>0.616</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.4513</v>
+        <v>-0.3555</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.5928</v>
+        <v>-0.4882</v>
       </c>
       <c r="U23" t="n">
-        <v>0.1415</v>
+        <v>0.1328</v>
       </c>
       <c r="V23" t="n">
         <v>-0.2402</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>8.330599999999999</v>
+        <v>9.027900000000001</v>
       </c>
       <c r="E24" t="n">
         <v>16.5354</v>
       </c>
       <c r="F24" t="n">
-        <v>-8.205</v>
+        <v>-7.5076</v>
       </c>
       <c r="G24" t="n">
         <v>14.1543</v>
@@ -2326,13 +2326,13 @@
         <v>13.3471</v>
       </c>
       <c r="S24" t="n">
-        <v>-3.448</v>
+        <v>-2.7508</v>
       </c>
       <c r="T24" t="n">
         <v>-4.0113</v>
       </c>
       <c r="U24" t="n">
-        <v>0.5631999999999999</v>
+        <v>1.2605</v>
       </c>
       <c r="V24" t="n">
         <v>-6.4824</v>
